--- a/MR_gwas/gMR_dat.xlsx
+++ b/MR_gwas/gMR_dat.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="93">
   <si>
     <t>SNP</t>
   </si>
@@ -191,106 +191,112 @@
     <t>17</t>
   </si>
   <si>
+    <t>41773814</t>
+  </si>
+  <si>
+    <t>41777862</t>
+  </si>
+  <si>
+    <t>41789965</t>
+  </si>
+  <si>
+    <t>41798621</t>
+  </si>
+  <si>
+    <t>41801263</t>
+  </si>
+  <si>
+    <t>41808374</t>
+  </si>
+  <si>
+    <t>Heel bone mineral density || id:ebi-a-GCST006979</t>
+  </si>
+  <si>
+    <t>Heel bone mineral density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heel bone mineral density ||  || </t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>igd</t>
+  </si>
+  <si>
+    <t>rs1107748</t>
+  </si>
+  <si>
+    <t>Sclerostin</t>
+  </si>
+  <si>
+    <t>chromosome</t>
+  </si>
+  <si>
+    <t>base_pair_location</t>
+  </si>
+  <si>
+    <t>Hip fracture</t>
+  </si>
+  <si>
+    <t>ebi-a-GCST005194</t>
+  </si>
+  <si>
+    <t>41772813</t>
+  </si>
+  <si>
+    <t>Coronary artery disease || id:ebi-a-GCST005194</t>
+  </si>
+  <si>
+    <t>Coronary artery disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronary artery disease ||  || </t>
+  </si>
+  <si>
+    <t>ebi-a-GCST011365</t>
+  </si>
+  <si>
+    <t>Myocardial infarction || id:ebi-a-GCST011365</t>
+  </si>
+  <si>
+    <t>Myocardial infarction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myocardial infarction ||  || </t>
+  </si>
+  <si>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>ukb-b-14057</t>
+  </si>
+  <si>
+    <t>Non-cancer illness code, self-reported: hypertension || id:ukb-b-14057</t>
+  </si>
+  <si>
+    <t>Non-cancer illness code, self-reported: hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-cancer illness code, self-reported: hypertension ||  || </t>
+  </si>
+  <si>
+    <t>ebi-a-GCST006867</t>
+  </si>
+  <si>
     <t>41774270</t>
   </si>
   <si>
-    <t>41777862</t>
-  </si>
-  <si>
-    <t>41789965</t>
-  </si>
-  <si>
-    <t>41798621</t>
-  </si>
-  <si>
-    <t>41801263</t>
-  </si>
-  <si>
-    <t>41808374</t>
-  </si>
-  <si>
-    <t>Heel bone mineral density || id:ebi-a-GCST006979</t>
-  </si>
-  <si>
-    <t>Heel bone mineral density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heel bone mineral density ||  || </t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>igd</t>
+    <t>Type 2 diabetes || id:ebi-a-GCST006867</t>
+  </si>
+  <si>
+    <t>Type 2 diabetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type 2 diabetes ||  || </t>
   </si>
   <si>
     <t>rs1107747</t>
-  </si>
-  <si>
-    <t>Sclerostin</t>
-  </si>
-  <si>
-    <t>chromosome</t>
-  </si>
-  <si>
-    <t>base_pair_location</t>
-  </si>
-  <si>
-    <t>Hip fracture</t>
-  </si>
-  <si>
-    <t>ebi-a-GCST005194</t>
-  </si>
-  <si>
-    <t>41772813</t>
-  </si>
-  <si>
-    <t>Coronary artery disease || id:ebi-a-GCST005194</t>
-  </si>
-  <si>
-    <t>Coronary artery disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronary artery disease ||  || </t>
-  </si>
-  <si>
-    <t>ebi-a-GCST011365</t>
-  </si>
-  <si>
-    <t>Myocardial infarction || id:ebi-a-GCST011365</t>
-  </si>
-  <si>
-    <t>Myocardial infarction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myocardial infarction ||  || </t>
-  </si>
-  <si>
-    <t>IS</t>
-  </si>
-  <si>
-    <t>ukb-b-14057</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported: hypertension || id:ukb-b-14057</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported: hypertension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-cancer illness code, self-reported: hypertension ||  || </t>
-  </si>
-  <si>
-    <t>ebi-a-GCST006867</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes || id:ebi-a-GCST006867</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type 2 diabetes ||  || </t>
   </si>
 </sst>
 </file>
@@ -478,13 +484,13 @@
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0349833</v>
+        <v>-0.0346809</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.609298</v>
+        <v>0.608329</v>
       </c>
       <c r="K2" t="s">
         <v>54</v>
@@ -505,13 +511,13 @@
         <v>57</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00190023</v>
+        <v>0.00189411</v>
       </c>
       <c r="R2" t="n">
         <v>426824.0</v>
       </c>
       <c r="S2" t="n">
-        <v>6.4003E-58</v>
+        <v>2.19989E-57</v>
       </c>
       <c r="T2" t="s">
         <v>63</v>
@@ -4603,7 +4609,7 @@
         <v>56</v>
       </c>
       <c r="P2" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0081</v>
@@ -4615,13 +4621,13 @@
         <v>0.2432</v>
       </c>
       <c r="T2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W2" t="s">
         <v>66</v>
@@ -4636,7 +4642,7 @@
         <v>44</v>
       </c>
       <c r="AA2" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="AB2" t="s">
         <v>52</v>
@@ -4734,13 +4740,13 @@
         <v>0.23</v>
       </c>
       <c r="T3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W3" t="s">
         <v>66</v>
@@ -4853,13 +4859,13 @@
         <v>0.1725</v>
       </c>
       <c r="T4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W4" t="s">
         <v>66</v>
@@ -4972,13 +4978,13 @@
         <v>0.1318</v>
       </c>
       <c r="T5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W5" t="s">
         <v>66</v>
@@ -5091,13 +5097,13 @@
         <v>0.9881</v>
       </c>
       <c r="T6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="U6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="V6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="W6" t="s">
         <v>66</v>

--- a/MR_gwas/gMR_dat.xlsx
+++ b/MR_gwas/gMR_dat.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="93">
   <si>
     <t>SNP</t>
   </si>
@@ -128,6 +128,12 @@
     <t>exposure</t>
   </si>
   <si>
+    <t>beta.exposure_corrected</t>
+  </si>
+  <si>
+    <t>se.exposure_corrected</t>
+  </si>
+  <si>
     <t>action</t>
   </si>
   <si>
@@ -284,9 +290,6 @@
     <t>ebi-a-GCST006867</t>
   </si>
   <si>
-    <t>41774270</t>
-  </si>
-  <si>
     <t>Type 2 diabetes || id:ebi-a-GCST006867</t>
   </si>
   <si>
@@ -294,9 +297,6 @@
   </si>
   <si>
     <t xml:space="preserve">Type 2 diabetes ||  || </t>
-  </si>
-  <si>
-    <t>rs1107747</t>
   </si>
 </sst>
 </file>
@@ -460,28 +460,34 @@
       <c r="AM1" t="s">
         <v>37</v>
       </c>
+      <c r="AN1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0346809</v>
@@ -493,22 +499,22 @@
         <v>0.608329</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q2" t="n">
         <v>0.00189411</v>
@@ -520,40 +526,40 @@
         <v>2.19989E-57</v>
       </c>
       <c r="T2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC2" t="s">
         <v>52</v>
       </c>
-      <c r="AC2" t="s">
-        <v>50</v>
-      </c>
       <c r="AD2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE2" t="s">
         <v>52</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>50</v>
       </c>
       <c r="AF2" t="n">
         <v>1.0</v>
@@ -568,39 +574,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AJ2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM2" t="s">
-        <v>66</v>
+      <c r="AO2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.0327884</v>
@@ -612,22 +624,22 @@
         <v>0.358972</v>
       </c>
       <c r="K3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
         <v>0.00194008</v>
@@ -639,19 +651,19 @@
         <v>4.40048E-49</v>
       </c>
       <c r="T3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y3" t="e">
         <v>#N/A</v>
@@ -687,39 +699,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AJ3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM3" t="s">
-        <v>66</v>
+      <c r="AO3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.0389008</v>
@@ -731,22 +749,22 @@
         <v>0.614724</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="n">
         <v>0.00191171</v>
@@ -758,19 +776,19 @@
         <v>3.90032E-70</v>
       </c>
       <c r="T4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="e">
         <v>#N/A</v>
@@ -806,39 +824,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AJ4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM4" t="s">
-        <v>66</v>
+      <c r="AO4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.0733786</v>
@@ -850,22 +874,22 @@
         <v>0.081972</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="n">
         <v>0.00345075</v>
@@ -877,19 +901,19 @@
         <v>1.0E-85</v>
       </c>
       <c r="T5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y5" t="e">
         <v>#N/A</v>
@@ -925,39 +949,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="AJ5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AN5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM5" t="s">
-        <v>66</v>
+      <c r="AO5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.0411364</v>
@@ -969,22 +999,22 @@
         <v>0.3193</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
         <v>0.00200799</v>
@@ -996,19 +1026,19 @@
         <v>7.10068E-73</v>
       </c>
       <c r="T6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y6" t="e">
         <v>#N/A</v>
@@ -1044,39 +1074,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AJ6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="AN6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM6" t="s">
-        <v>66</v>
+      <c r="AO6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.0743817</v>
@@ -1088,22 +1124,22 @@
         <v>0.08288</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00336822</v>
@@ -1115,19 +1151,19 @@
         <v>4.40048E-88</v>
       </c>
       <c r="T7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="U7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="W7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y7" t="e">
         <v>#N/A</v>
@@ -1163,16 +1199,22 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AJ7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AN7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM7" t="s">
-        <v>66</v>
+      <c r="AO7" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1230,10 +1272,10 @@
         <v>17</v>
       </c>
       <c r="P1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="Q1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R1" t="s">
         <v>15</v>
@@ -1266,30 +1308,36 @@
         <v>37</v>
       </c>
       <c r="AB1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.058</v>
@@ -1301,16 +1349,16 @@
         <v>0.5608</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O2" t="n">
         <v>1.164E-4</v>
@@ -1325,7 +1373,7 @@
         <v>0.0151</v>
       </c>
       <c r="S2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T2" t="n">
         <v>1.0</v>
@@ -1340,42 +1388,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="X2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="AB2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA2" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB2" t="e">
+      <c r="AC2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0519</v>
@@ -1387,16 +1441,16 @@
         <v>0.3735</v>
       </c>
       <c r="K3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O3" t="n">
         <v>6.709E-4</v>
@@ -1411,7 +1465,7 @@
         <v>0.0153</v>
       </c>
       <c r="S3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T3" t="n">
         <v>2.0</v>
@@ -1426,42 +1480,48 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="X3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA3" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB3" t="e">
+      <c r="AC3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>0.0706</v>
@@ -1473,16 +1533,16 @@
         <v>0.5828</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O4" t="n">
         <v>2.354E-6</v>
@@ -1497,7 +1557,7 @@
         <v>0.015</v>
       </c>
       <c r="S4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T4" t="n">
         <v>3.0</v>
@@ -1512,42 +1572,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="X4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AB4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB4" t="e">
+      <c r="AC4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.1444</v>
@@ -1559,16 +1625,16 @@
         <v>0.0865</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O5" t="n">
         <v>2.586E-6</v>
@@ -1583,7 +1649,7 @@
         <v>0.0307</v>
       </c>
       <c r="S5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T5" t="n">
         <v>4.0</v>
@@ -1598,42 +1664,48 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="X5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA5" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB5" t="e">
+      <c r="AC5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.0721</v>
@@ -1645,16 +1717,16 @@
         <v>0.3404</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O6" t="n">
         <v>3.78E-6</v>
@@ -1669,7 +1741,7 @@
         <v>0.0156</v>
       </c>
       <c r="S6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T6" t="n">
         <v>5.0</v>
@@ -1684,42 +1756,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="X6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="AB6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA6" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB6" t="e">
+      <c r="AC6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.1312</v>
@@ -1731,16 +1809,16 @@
         <v>0.098</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O7" t="n">
         <v>2.023E-7</v>
@@ -1755,7 +1833,7 @@
         <v>0.0253</v>
       </c>
       <c r="S7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="T7" t="n">
         <v>6.0</v>
@@ -1770,18 +1848,24 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="X7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Y7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Z7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AB7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AA7" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB7" t="e">
+      <c r="AC7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AD7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1890,28 +1974,34 @@
       <c r="AF1" t="s">
         <v>37</v>
       </c>
+      <c r="AG1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0073</v>
@@ -1923,22 +2013,22 @@
         <v>0.5563</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0059</v>
@@ -1950,19 +2040,19 @@
         <v>0.2177</v>
       </c>
       <c r="T2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="U2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y2" t="n">
         <v>1.0</v>
@@ -1977,39 +2067,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AC2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF2" t="s">
-        <v>66</v>
+      <c r="AH2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.0081</v>
@@ -2021,22 +2117,22 @@
         <v>0.368</v>
       </c>
       <c r="K3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0059</v>
@@ -2048,19 +2144,19 @@
         <v>0.1696</v>
       </c>
       <c r="T3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="U3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y3" t="n">
         <v>2.0</v>
@@ -2075,39 +2171,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AC3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF3" t="s">
-        <v>66</v>
+      <c r="AH3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.0115</v>
@@ -2119,22 +2221,22 @@
         <v>0.5991</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0058</v>
@@ -2146,19 +2248,19 @@
         <v>0.0456604</v>
       </c>
       <c r="T4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="U4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="n">
         <v>3.0</v>
@@ -2173,39 +2275,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AC4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF4" t="s">
-        <v>66</v>
+      <c r="AH4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.0131</v>
@@ -2217,22 +2325,22 @@
         <v>0.0795</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0111</v>
@@ -2244,19 +2352,19 @@
         <v>0.2391</v>
       </c>
       <c r="T5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y5" t="n">
         <v>4.0</v>
@@ -2271,39 +2379,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="AC5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF5" t="s">
-        <v>66</v>
+      <c r="AH5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.0145</v>
@@ -2315,22 +2429,22 @@
         <v>0.307</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0062</v>
@@ -2342,19 +2456,19 @@
         <v>0.0199802</v>
       </c>
       <c r="T6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="U6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y6" t="n">
         <v>5.0</v>
@@ -2369,39 +2483,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AC6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF6" t="s">
-        <v>66</v>
+      <c r="AH6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.0116</v>
@@ -2413,22 +2533,22 @@
         <v>0.0747</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q7" t="n">
         <v>0.0111</v>
@@ -2440,19 +2560,19 @@
         <v>0.2969</v>
       </c>
       <c r="T7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="U7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="V7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="W7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y7" t="n">
         <v>6.0</v>
@@ -2467,16 +2587,22 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AC7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF7" t="s">
-        <v>66</v>
+      <c r="AH7" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2584,28 +2710,34 @@
       <c r="AF1" t="s">
         <v>37</v>
       </c>
+      <c r="AG1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.011909</v>
@@ -2617,22 +2749,22 @@
         <v>0.561269</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q2" t="n">
         <v>0.007812</v>
@@ -2644,19 +2776,19 @@
         <v>0.127364</v>
       </c>
       <c r="T2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y2" t="n">
         <v>1.0</v>
@@ -2671,39 +2803,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AC2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF2" t="s">
-        <v>66</v>
+      <c r="AH2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.009864</v>
@@ -2715,22 +2853,22 @@
         <v>0.362718</v>
       </c>
       <c r="K3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
         <v>0.007769</v>
@@ -2742,19 +2880,19 @@
         <v>0.204175</v>
       </c>
       <c r="T3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y3" t="n">
         <v>2.0</v>
@@ -2769,39 +2907,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AC3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF3" t="s">
-        <v>66</v>
+      <c r="AH3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.010354</v>
@@ -2813,22 +2957,22 @@
         <v>0.6033580000000001</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="n">
         <v>0.007615</v>
@@ -2840,19 +2984,19 @@
         <v>0.173892</v>
       </c>
       <c r="T4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="n">
         <v>3.0</v>
@@ -2867,39 +3011,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AC4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF4" t="s">
-        <v>66</v>
+      <c r="AH4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.027632</v>
@@ -2911,22 +3061,22 @@
         <v>0.076448</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="n">
         <v>0.015085</v>
@@ -2938,19 +3088,19 @@
         <v>0.0670054</v>
       </c>
       <c r="T5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y5" t="n">
         <v>4.0</v>
@@ -2965,39 +3115,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="AC5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF5" t="s">
-        <v>66</v>
+      <c r="AH5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.012524</v>
@@ -3009,22 +3165,22 @@
         <v>0.29944</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
         <v>0.008282</v>
@@ -3036,19 +3192,19 @@
         <v>0.130477</v>
       </c>
       <c r="T6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y6" t="n">
         <v>5.0</v>
@@ -3063,39 +3219,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AC6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF6" t="s">
-        <v>66</v>
+      <c r="AH6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.03107</v>
@@ -3107,22 +3269,22 @@
         <v>0.071269</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q7" t="n">
         <v>0.014973</v>
@@ -3134,19 +3296,19 @@
         <v>0.0379962</v>
       </c>
       <c r="T7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="U7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="W7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y7" t="n">
         <v>6.0</v>
@@ -3161,16 +3323,22 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AC7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF7" t="s">
-        <v>66</v>
+      <c r="AH7" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -3258,30 +3426,36 @@
         <v>37</v>
       </c>
       <c r="Z1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.0128</v>
@@ -3293,16 +3467,16 @@
         <v>0.5619</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O2" t="n">
         <v>0.0075</v>
@@ -3311,7 +3485,7 @@
         <v>0.08812</v>
       </c>
       <c r="Q2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R2" t="n">
         <v>1.0</v>
@@ -3326,42 +3500,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.0052</v>
@@ -3373,16 +3553,16 @@
         <v>0.3711</v>
       </c>
       <c r="K3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O3" t="n">
         <v>0.0075</v>
@@ -3391,7 +3571,7 @@
         <v>0.4928</v>
       </c>
       <c r="Q3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R3" t="n">
         <v>2.0</v>
@@ -3406,42 +3586,48 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.0117</v>
@@ -3453,16 +3639,16 @@
         <v>0.5896</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O4" t="n">
         <v>0.0071</v>
@@ -3471,7 +3657,7 @@
         <v>0.1022</v>
       </c>
       <c r="Q4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R4" t="n">
         <v>3.0</v>
@@ -3486,42 +3672,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.0041</v>
@@ -3533,16 +3725,16 @@
         <v>0.0844</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O5" t="n">
         <v>0.0144</v>
@@ -3551,7 +3743,7 @@
         <v>0.778</v>
       </c>
       <c r="Q5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R5" t="n">
         <v>4.0</v>
@@ -3566,42 +3758,48 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.0037</v>
@@ -3613,16 +3811,16 @@
         <v>0.3322</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O6" t="n">
         <v>0.0074</v>
@@ -3631,7 +3829,7 @@
         <v>0.6207</v>
       </c>
       <c r="Q6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R6" t="n">
         <v>5.0</v>
@@ -3646,42 +3844,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.0055</v>
@@ -3693,16 +3897,16 @@
         <v>0.0935</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O7" t="n">
         <v>0.0125</v>
@@ -3711,7 +3915,7 @@
         <v>0.6618</v>
       </c>
       <c r="Q7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R7" t="n">
         <v>6.0</v>
@@ -3726,18 +3930,24 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3846,28 +4056,34 @@
       <c r="AF1" t="s">
         <v>37</v>
       </c>
+      <c r="AG1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-3.57131E-4</v>
@@ -3879,22 +4095,22 @@
         <v>0.575037</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q2" t="n">
         <v>9.31355E-4</v>
@@ -3906,19 +4122,19 @@
         <v>0.7</v>
       </c>
       <c r="T2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y2" t="n">
         <v>1.0</v>
@@ -3933,39 +4149,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AC2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="AG2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF2" t="s">
-        <v>66</v>
+      <c r="AH2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>5.24138E-4</v>
@@ -3977,22 +4199,22 @@
         <v>0.360018</v>
       </c>
       <c r="K3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
         <v>9.41774E-4</v>
@@ -4004,19 +4226,19 @@
         <v>0.58</v>
       </c>
       <c r="T3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y3" t="n">
         <v>2.0</v>
@@ -4031,39 +4253,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AC3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF3" t="s">
-        <v>66</v>
+      <c r="AH3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-5.73167E-4</v>
@@ -4075,22 +4303,22 @@
         <v>0.613402</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="n">
         <v>9.27905E-4</v>
@@ -4102,19 +4330,19 @@
         <v>0.54</v>
       </c>
       <c r="T4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="n">
         <v>3.0</v>
@@ -4129,39 +4357,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AC4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF4" t="s">
-        <v>66</v>
+      <c r="AH4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.00299558</v>
@@ -4173,22 +4407,22 @@
         <v>0.08108</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0016853</v>
@@ -4200,19 +4434,19 @@
         <v>0.0749998</v>
       </c>
       <c r="T5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y5" t="n">
         <v>4.0</v>
@@ -4227,39 +4461,45 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="AC5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.0282632653061224</v>
+      </c>
+      <c r="AG5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF5" t="s">
-        <v>66</v>
+      <c r="AH5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" t="s">
-        <v>51</v>
-      </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.00125623</v>
@@ -4271,22 +4511,22 @@
         <v>0.320025</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q6" t="n">
         <v>9.74984E-4</v>
@@ -4298,19 +4538,19 @@
         <v>0.2</v>
       </c>
       <c r="T6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y6" t="n">
         <v>5.0</v>
@@ -4325,39 +4565,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AC6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="AG6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF6" t="s">
-        <v>66</v>
+      <c r="AH6" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" t="s">
-        <v>50</v>
-      </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.0015747</v>
@@ -4369,22 +4615,22 @@
         <v>0.081717</v>
       </c>
       <c r="K7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q7" t="n">
         <v>0.00164674</v>
@@ -4396,19 +4642,19 @@
         <v>0.34</v>
       </c>
       <c r="T7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="V7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="W7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y7" t="n">
         <v>6.0</v>
@@ -4423,16 +4669,22 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AC7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AD7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AE7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.0</v>
       </c>
-      <c r="AF7" t="s">
-        <v>66</v>
+      <c r="AH7" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4561,100 +4813,106 @@
       <c r="AM1" t="s">
         <v>37</v>
       </c>
+      <c r="AN1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
         <v>52</v>
       </c>
-      <c r="E2" t="s">
-        <v>50</v>
-      </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0094</v>
+        <v>-0.0101</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.608197</v>
+        <v>0.6061639999999999</v>
       </c>
       <c r="K2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0081</v>
+        <v>0.0079</v>
       </c>
       <c r="R2" t="n">
         <v>62892.0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2432</v>
+        <v>0.2041</v>
       </c>
       <c r="T2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Z2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC2" t="s">
         <v>52</v>
       </c>
-      <c r="AC2" t="s">
-        <v>50</v>
-      </c>
       <c r="AD2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE2" t="s">
         <v>52</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>50</v>
       </c>
       <c r="AF2" t="n">
         <v>1.0</v>
@@ -4669,39 +4927,45 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="AJ2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="AN2" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM2" t="s">
-        <v>66</v>
+      <c r="AO2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" t="s">
         <v>52</v>
       </c>
-      <c r="E3" t="s">
-        <v>50</v>
-      </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.0099</v>
@@ -4713,22 +4977,22 @@
         <v>0.358299</v>
       </c>
       <c r="K3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="Q3" t="n">
         <v>0.0082</v>
@@ -4740,19 +5004,19 @@
         <v>0.23</v>
       </c>
       <c r="T3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y3" t="e">
         <v>#N/A</v>
@@ -4788,39 +5052,45 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="AJ3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0144209183673469</v>
+      </c>
+      <c r="AN3" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM3" t="s">
-        <v>66</v>
+      <c r="AO3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.0109</v>
@@ -4832,22 +5102,22 @@
         <v>0.6135740000000001</v>
       </c>
       <c r="K4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q4" t="n">
         <v>0.008</v>
@@ -4859,19 +5129,19 @@
         <v>0.1725</v>
       </c>
       <c r="T4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y4" t="e">
         <v>#N/A</v>
@@ -4907,39 +5177,45 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="AJ4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="AN4" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM4" t="s">
-        <v>66</v>
+      <c r="AO4" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
         <v>53</v>
       </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H5" t="n">
         <v>0.0129</v>
@@ -4951,22 +5227,22 @@
         <v>0.315314</v>
       </c>
       <c r="K5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0085</v>
@@ -4978,19 +5254,19 @@
         <v>0.1318</v>
       </c>
       <c r="T5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y5" t="e">
         <v>#N/A</v>
@@ -5026,39 +5302,45 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="AJ5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL5" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="AN5" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM5" t="s">
-        <v>66</v>
+      <c r="AO5" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" t="s">
         <v>52</v>
       </c>
-      <c r="E6" t="s">
-        <v>50</v>
-      </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" t="n">
-        <v>0.060792</v>
+        <v>-0.060792</v>
       </c>
       <c r="H6" t="n">
         <v>-2.0E-4</v>
@@ -5070,22 +5352,22 @@
         <v>0.0801682</v>
       </c>
       <c r="K6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="P6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q6" t="n">
         <v>0.0146</v>
@@ -5097,19 +5379,19 @@
         <v>0.9881</v>
       </c>
       <c r="T6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="U6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="V6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="W6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="X6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Y6" t="e">
         <v>#N/A</v>
@@ -5145,16 +5427,22 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="AJ6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AK6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AL6" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0245357142857143</v>
+      </c>
+      <c r="AN6" t="n">
         <v>2.0</v>
       </c>
-      <c r="AM6" t="s">
-        <v>66</v>
+      <c r="AO6" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/MR_gwas/gMR_dat.xlsx
+++ b/MR_gwas/gMR_dat.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="95">
   <si>
     <t>SNP</t>
   </si>
@@ -197,106 +197,112 @@
     <t>17</t>
   </si>
   <si>
+    <t>41774270</t>
+  </si>
+  <si>
+    <t>41777862</t>
+  </si>
+  <si>
+    <t>41789965</t>
+  </si>
+  <si>
+    <t>41798621</t>
+  </si>
+  <si>
+    <t>41801263</t>
+  </si>
+  <si>
+    <t>41808374</t>
+  </si>
+  <si>
+    <t>Heel bone mineral density || id:ebi-a-GCST006979</t>
+  </si>
+  <si>
+    <t>Heel bone mineral density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heel bone mineral density ||  || </t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>igd</t>
+  </si>
+  <si>
+    <t>rs1107747</t>
+  </si>
+  <si>
+    <t>Sclerostin</t>
+  </si>
+  <si>
+    <t>chromosome</t>
+  </si>
+  <si>
+    <t>base_pair_location</t>
+  </si>
+  <si>
+    <t>Hip fracture</t>
+  </si>
+  <si>
+    <t>ebi-a-GCST005194</t>
+  </si>
+  <si>
+    <t>41772813</t>
+  </si>
+  <si>
+    <t>Coronary artery disease || id:ebi-a-GCST005194</t>
+  </si>
+  <si>
+    <t>Coronary artery disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coronary artery disease ||  || </t>
+  </si>
+  <si>
+    <t>ebi-a-GCST011365</t>
+  </si>
+  <si>
+    <t>Myocardial infarction || id:ebi-a-GCST011365</t>
+  </si>
+  <si>
+    <t>Myocardial infarction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myocardial infarction ||  || </t>
+  </si>
+  <si>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>ukb-b-14057</t>
+  </si>
+  <si>
+    <t>Non-cancer illness code, self-reported: hypertension || id:ukb-b-14057</t>
+  </si>
+  <si>
+    <t>Non-cancer illness code, self-reported: hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-cancer illness code, self-reported: hypertension ||  || </t>
+  </si>
+  <si>
+    <t>ebi-a-GCST006867</t>
+  </si>
+  <si>
     <t>41773814</t>
   </si>
   <si>
-    <t>41777862</t>
-  </si>
-  <si>
-    <t>41789965</t>
-  </si>
-  <si>
-    <t>41798621</t>
-  </si>
-  <si>
-    <t>41801263</t>
-  </si>
-  <si>
-    <t>41808374</t>
-  </si>
-  <si>
-    <t>Heel bone mineral density || id:ebi-a-GCST006979</t>
-  </si>
-  <si>
-    <t>Heel bone mineral density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heel bone mineral density ||  || </t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>igd</t>
+    <t>Type 2 diabetes || id:ebi-a-GCST006867</t>
+  </si>
+  <si>
+    <t>Type 2 diabetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type 2 diabetes ||  || </t>
   </si>
   <si>
     <t>rs1107748</t>
-  </si>
-  <si>
-    <t>Sclerostin</t>
-  </si>
-  <si>
-    <t>chromosome</t>
-  </si>
-  <si>
-    <t>base_pair_location</t>
-  </si>
-  <si>
-    <t>Hip fracture</t>
-  </si>
-  <si>
-    <t>ebi-a-GCST005194</t>
-  </si>
-  <si>
-    <t>41772813</t>
-  </si>
-  <si>
-    <t>Coronary artery disease || id:ebi-a-GCST005194</t>
-  </si>
-  <si>
-    <t>Coronary artery disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coronary artery disease ||  || </t>
-  </si>
-  <si>
-    <t>ebi-a-GCST011365</t>
-  </si>
-  <si>
-    <t>Myocardial infarction || id:ebi-a-GCST011365</t>
-  </si>
-  <si>
-    <t>Myocardial infarction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Myocardial infarction ||  || </t>
-  </si>
-  <si>
-    <t>IS</t>
-  </si>
-  <si>
-    <t>ukb-b-14057</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported: hypertension || id:ukb-b-14057</t>
-  </si>
-  <si>
-    <t>Non-cancer illness code, self-reported: hypertension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-cancer illness code, self-reported: hypertension ||  || </t>
-  </si>
-  <si>
-    <t>ebi-a-GCST006867</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes || id:ebi-a-GCST006867</t>
-  </si>
-  <si>
-    <t>Type 2 diabetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Type 2 diabetes ||  || </t>
   </si>
 </sst>
 </file>
@@ -490,13 +496,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0346809</v>
+        <v>-0.0349833</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.608329</v>
+        <v>0.609298</v>
       </c>
       <c r="K2" t="s">
         <v>56</v>
@@ -517,13 +523,13 @@
         <v>59</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00189411</v>
+        <v>0.00190023</v>
       </c>
       <c r="R2" t="n">
         <v>426824.0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.19989E-57</v>
+        <v>6.4003E-58</v>
       </c>
       <c r="T2" t="s">
         <v>65</v>
@@ -4867,7 +4873,7 @@
         <v>58</v>
       </c>
       <c r="P2" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="Q2" t="n">
         <v>0.0079</v>
@@ -4879,13 +4885,13 @@
         <v>0.2041</v>
       </c>
       <c r="T2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W2" t="s">
         <v>68</v>
@@ -4900,7 +4906,7 @@
         <v>46</v>
       </c>
       <c r="AA2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="AB2" t="s">
         <v>54</v>
@@ -5004,13 +5010,13 @@
         <v>0.23</v>
       </c>
       <c r="T3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W3" t="s">
         <v>68</v>
@@ -5129,13 +5135,13 @@
         <v>0.1725</v>
       </c>
       <c r="T4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W4" t="s">
         <v>68</v>
@@ -5254,13 +5260,13 @@
         <v>0.1318</v>
       </c>
       <c r="T5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W5" t="s">
         <v>68</v>
@@ -5379,13 +5385,13 @@
         <v>0.9881</v>
       </c>
       <c r="T6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="U6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="V6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="W6" t="s">
         <v>68</v>
